--- a/notebooks/review.xlsx
+++ b/notebooks/review.xlsx
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="208">
+  <si>
+    <t>№</t>
+  </si>
   <si>
     <t>статья</t>
   </si>
@@ -45,9 +48,6 @@
     <t>ссылка</t>
   </si>
   <si>
-    <t>№</t>
-  </si>
-  <si>
     <t>OpenTag, KDD 2018</t>
   </si>
   <si>
@@ -57,7 +57,10 @@
     <t>MAVE, WSDM 2022</t>
   </si>
   <si>
-    <t>ExtractGPT, 2023 (препринт)</t>
+    <t>Roy, Goyal, Pandey. Exploring generative frameworks for product attribute value extraction, Expert Systems with Applications, т. 243, 2024, Q1 по Scimago (SJR 2025 = 1,939)</t>
+  </si>
+  <si>
+    <t>ExtractGPT, iiWAS 2024 (препринт 2023)</t>
   </si>
   <si>
     <t>Brinkmann и др., 2024 (препринт)</t>
@@ -66,18 +69,15 @@
     <t>GAVEL, 2025</t>
   </si>
   <si>
+    <t>Çiftlikçi и др., Electronics (MDPI) 2025, Q2 по Scimago (SJR 2025 = 0,623)</t>
+  </si>
+  <si>
     <t>SynthIE, EMNLP 2023</t>
   </si>
   <si>
     <t>Controlled Product Generation, 2025 (препринт)</t>
   </si>
   <si>
-    <t>JSONSchemaBench, 2025 (препринт)</t>
-  </si>
-  <si>
-    <t>Structured Output Benchmark, 2026 (препринт)</t>
-  </si>
-  <si>
     <t>Qwen2.5, 2024 (препринт)</t>
   </si>
   <si>
@@ -90,9 +90,6 @@
     <t>QLoRA, NeurIPS 2023</t>
   </si>
   <si>
-    <t>Wildberries, Habr 2025</t>
-  </si>
-  <si>
     <t>достать значения из текста</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
     <t>большой датасет</t>
   </si>
   <si>
+    <t>достать значение атрибута генерацией, а не разметкой токенов или вопросами-ответами</t>
+  </si>
+  <si>
     <t>то же, но через LLM</t>
   </si>
   <si>
@@ -111,18 +111,15 @@
     <t>извлекать и обучаться на данных, дополненных LLM</t>
   </si>
   <si>
+    <t>извлечение атрибутов из турецких карточек Trendyol</t>
+  </si>
+  <si>
     <t>синтетика для извлечения</t>
   </si>
   <si>
     <t>синтетические товары</t>
   </si>
   <si>
-    <t>заставить модель отвечать по JSON-схеме</t>
-  </si>
-  <si>
-    <t>проверка JSON-ответов</t>
-  </si>
-  <si>
     <t>модели</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>то же, но ещё дешевле</t>
   </si>
   <si>
-    <t>сопоставление товаров, одним из шагов извлекают атрибуты</t>
-  </si>
-  <si>
     <t>BiLSTM-CRF + attention, активное обучение</t>
   </si>
   <si>
@@ -147,6 +141,9 @@
     <t>модель + датасет</t>
   </si>
   <si>
+    <t>две постановки: (1) по названию и атрибуту сгенерировать значение; (2) по названию сразу выдать пары «атрибут-значение» (словами или позициями); BART, T5, WDec, PNDec (в ESWA ещё GPT-2, FLAN-T5)</t>
+  </si>
+  <si>
     <t>промпт: описание атрибута + примеры значений + примеры разбора</t>
   </si>
   <si>
@@ -156,18 +153,15 @@
     <t>генерация + LLM</t>
   </si>
   <si>
+    <t>Mistral + LoRA (rank 64, alpha 128) против RoBERTa</t>
+  </si>
+  <si>
     <t>сначала готовая структура, потом LLM пишет по ней текст; на этом учат малые модели</t>
   </si>
   <si>
     <t>LLM пишет товары по заданным атрибутам</t>
   </si>
   <si>
-    <t>сравнение 6 способов строгого формата</t>
-  </si>
-  <si>
-    <t>21 модель, 7 метрик</t>
-  </si>
-  <si>
     <t>Transformer, 18 трлн токенов</t>
   </si>
   <si>
@@ -180,9 +174,6 @@
     <t>4-битная модель + LoRA</t>
   </si>
   <si>
-    <t>Qwen2.5-72B без примеров, ОЗУ/ПЗУ переводят в ГБ</t>
-  </si>
-  <si>
     <t>Amazon.com: корм для собак, камеры, моющие средства</t>
   </si>
   <si>
@@ -192,6 +183,9 @@
     <t>~2,2 млн товаров Amazon, 1257 категорий</t>
   </si>
   <si>
+    <t>AE-650K (AliExpress, Sports &amp; Entertainment) и MAE; 28 тыс. и 78 тыс. названий, 62 и 95 атрибутов; английский</t>
+  </si>
+  <si>
     <t>OA-Mine, AE-110K</t>
   </si>
   <si>
@@ -201,24 +195,18 @@
     <t>&gt;1000 атрибутов, 2000 категорий, тайский, вьетнамский, индонезийский</t>
   </si>
   <si>
+    <t>Trendyol, ~3 млн + ~867 тыс. записей, 700+ категорий и атрибутов, турецкий</t>
+  </si>
+  <si>
     <t>1,8 млн синтетических примеров</t>
   </si>
   <si>
     <t>синтетика + MAVE</t>
   </si>
   <si>
-    <t>10 000 JSON-схем</t>
-  </si>
-  <si>
-    <t>5000 текстов, плюс картинки и аудио</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
-    <t>закрытые данные маркетплейса</t>
-  </si>
-  <si>
     <t>F-score 83% (заявлено)</t>
   </si>
   <si>
@@ -228,6 +216,9 @@
     <t>Precision, Recall, F1 (усреднение не указано)</t>
   </si>
   <si>
+    <t>P, R, F1 по парам атрибут-значение, точное совпадение; генеративные лучше разметки токенов на 2–5 пунктов F1</t>
+  </si>
+  <si>
     <t>F1 у GPT-4 около 85%</t>
   </si>
   <si>
@@ -237,18 +228,15 @@
     <t>recall, F1, A/B-тест</t>
   </si>
   <si>
+    <t>P, R, F1; разница F1 от 3% считалась значимой</t>
+  </si>
+  <si>
     <t>micro/macro-F1 (+57 п.п. заявлено)</t>
   </si>
   <si>
     <t>на MAVE 60,5% на синтетике и 60,8% на реальных; 2000 товаров оценили люди: 99,6% звучат естественно</t>
   </si>
   <si>
-    <t>покрытие, скорость, качество</t>
-  </si>
-  <si>
-    <t>точность значений до 83% на тексте</t>
-  </si>
-  <si>
     <t>общие тесты</t>
   </si>
   <si>
@@ -261,15 +249,15 @@
     <t>модель 65B помещается на одну GPU 48 ГБ</t>
   </si>
   <si>
-    <t>цифры считали для всей цепочки, не для атрибутов</t>
-  </si>
-  <si>
     <t>в статье не указан</t>
   </si>
   <si>
     <t>разметка и скрипты очистки открыты; лицензия CC BY-NC 4.0 (только некоммерческое)</t>
   </si>
   <si>
+    <t>обещан github.com/kalyani-roy/AVE (в статье 'will be available')</t>
+  </si>
+  <si>
     <t>да: github.com/wbsg-uni-mannheim/extractgpt</t>
   </si>
   <si>
@@ -279,10 +267,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>есть на GitHub</t>
-  </si>
-  <si>
-    <t>открыты</t>
+    <t>не указан</t>
   </si>
   <si>
     <t>веса открыты, лицензию смотреть в карточке модели</t>
@@ -294,9 +279,6 @@
     <t>открыт</t>
   </si>
   <si>
-    <t>нет</t>
-  </si>
-  <si>
     <t>находит только куски текста, единицы не приводит</t>
   </si>
   <si>
@@ -306,6 +288,9 @@
     <t>английский; авторы ExtractGPT пишут, что в разметке есть ошибки</t>
   </si>
   <si>
+    <t>размечены не все значения, верная генерация считается ошибкой; случайное разбиение по названиям; только названия товаров, не описания; значения цельным куском</t>
+  </si>
+  <si>
     <t>английский, платные модели</t>
   </si>
   <si>
@@ -315,18 +300,15 @@
     <t>какие данные и модели, не сказано</t>
   </si>
   <si>
+    <t>данные внутренние; описание DL-модели в статье непоследовательно</t>
+  </si>
+  <si>
     <t>другая область</t>
   </si>
   <si>
     <t>препринт, английский</t>
   </si>
   <si>
-    <t>схемы не про товары</t>
-  </si>
-  <si>
-    <t>не про товары</t>
-  </si>
-  <si>
     <t>про извлечение ничего</t>
   </si>
   <si>
@@ -339,9 +321,6 @@
     <t>качество оценивали через GPT-4</t>
   </si>
   <si>
-    <t>не рецензируется</t>
-  </si>
-  <si>
     <t>простая разметочная модель как baseline на русском</t>
   </si>
   <si>
@@ -351,6 +330,9 @@
     <t>формат записей, тест на новых атрибутах</t>
   </si>
   <si>
+    <t>формулировка «название + атрибут → значение» и предупреждение про неполную разметку (у нас в gold только значения из текста)</t>
+  </si>
+  <si>
     <t>взять шаблон промпта</t>
   </si>
   <si>
@@ -360,18 +342,15 @@
     <t>обучать на данных, которые дополнила LLM</t>
   </si>
   <si>
+    <t>LoRA на не-английском языке, ориентир гиперпараметров</t>
+  </si>
+  <si>
     <t>генерировать описания по готовым атрибутам: разметка известна сразу</t>
   </si>
   <si>
     <t>делать и примеры без части атрибутов (null)</t>
   </si>
   <si>
-    <t>отдельный прогон со строгим форматом</t>
-  </si>
-  <si>
-    <t>считать отдельно «JSON валидный» и «значения верные»</t>
-  </si>
-  <si>
     <t>кандидат в сравнение</t>
   </si>
   <si>
@@ -384,9 +363,6 @@
     <t>дообучение на 16–24 ГБ</t>
   </si>
   <si>
-    <t>приведение единиц; хватало около 100 размеченных примеров</t>
-  </si>
-  <si>
     <t>https://arxiv.org/abs/1806.01264</t>
   </si>
   <si>
@@ -396,6 +372,9 @@
     <t>https://research.google/pubs/mave-a-product-dataset-for-multi-source-attribute-value-extraction/</t>
   </si>
   <si>
+    <t>https://doi.org/10.1016/j.eswa.2023.122850</t>
+  </si>
+  <si>
     <t>https://arxiv.org/abs/2310.12537</t>
   </si>
   <si>
@@ -405,85 +384,127 @@
     <t>https://aclanthology.org/2025.knowledgenlp-1.6/</t>
   </si>
   <si>
+    <t>https://www.mdpi.com/2079-9292/14/10/1930</t>
+  </si>
+  <si>
     <t>https://aclanthology.org/2023.emnlp-main.96/</t>
   </si>
   <si>
     <t>https://arxiv.org/abs/2601.04200</t>
   </si>
   <si>
+    <t>https://arxiv.org/abs/2412.15115</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2025.acl-demo.10/</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2106.09685</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2305.14314</t>
+  </si>
+  <si>
+    <t>работа</t>
+  </si>
+  <si>
+    <t>почему выкинул</t>
+  </si>
+  <si>
+    <t>Vikhr (MRL 2024)</t>
+  </si>
+  <si>
+    <t>ruT5 / ruBERT (Zmitrovich и др.)</t>
+  </si>
+  <si>
+    <t>PAE</t>
+  </si>
+  <si>
+    <t>Habr, ecom.tech</t>
+  </si>
+  <si>
+    <t>UIE (ACL 2022)</t>
+  </si>
+  <si>
+    <t>OA-Mine (WWW 2022)</t>
+  </si>
+  <si>
+    <t>GPT-3 (NeurIPS 2020)</t>
+  </si>
+  <si>
+    <t>Parallel Decoding (Amazon)</t>
+  </si>
+  <si>
+    <t>Explicit Attribute Extraction in e-Commerce Search (ECNLP 2024)</t>
+  </si>
+  <si>
+    <t>Sabeh и др. Exploring LLMs for Product Attribute Value Identification (arXiv 2024)</t>
+  </si>
+  <si>
+    <t>Geng и др., JSONSchemaBench (arXiv 2025)</t>
+  </si>
+  <si>
+    <t>Singh и др., Structured Output Benchmark (arXiv 2026)</t>
+  </si>
+  <si>
+    <t>Кулиев, Habr (RWB), 2025</t>
+  </si>
+  <si>
+    <t>статью отозвали, в таблице 6 ошибка</t>
+  </si>
+  <si>
+    <t>модели общего назначения, про атрибуты ничего</t>
+  </si>
+  <si>
+    <t>извлекает из PDF с трендами моды, а не из описаний</t>
+  </si>
+  <si>
+    <t>про сопоставление товаров, не про извлечение</t>
+  </si>
+  <si>
+    <t>общее извлечение, не про товары</t>
+  </si>
+  <si>
+    <t>атрибуты заранее не заданы, а у нас заданы</t>
+  </si>
+  <si>
+    <t>общий фон, few-shot смотрим в ExtractGPT</t>
+  </si>
+  <si>
+    <t>нет даты и площадки, данные закрыты</t>
+  </si>
+  <si>
+    <t>извлекает из поисковых запросов, а не из описаний</t>
+  </si>
+  <si>
+    <t>промптинг LLaMA/Mistral для извлечения, близко к ExtractGPT и Brinkmann; в запас, лимит 10-15</t>
+  </si>
+  <si>
+    <t>про способы ограниченного декодирования (формат ответа модели), а обзор про качество извлечения; формат ответа проверяется в собственном эксперименте</t>
+  </si>
+  <si>
+    <t>про формат ответа модели на общих данных, не про извлечение атрибутов из товаров; формат проверяется в собственном эксперименте</t>
+  </si>
+  <si>
+    <t>не рецензируется; метрики относятся ко всему конвейеру сопоставления товаров, а не к извлечению атрибутов</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2024.ecnlp-1.13/</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2409.12695</t>
+  </si>
+  <si>
     <t>https://arxiv.org/abs/2501.10868</t>
   </si>
   <si>
     <t>https://arxiv.org/abs/2604.25359</t>
   </si>
   <si>
-    <t>https://arxiv.org/abs/2412.15115</t>
-  </si>
-  <si>
-    <t>https://aclanthology.org/2025.acl-demo.10/</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2106.09685</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2305.14314</t>
-  </si>
-  <si>
     <t>https://habr.com/ru/articles/911210</t>
   </si>
   <si>
-    <t>почему выкинул</t>
-  </si>
-  <si>
-    <t>работа</t>
-  </si>
-  <si>
-    <t>Vikhr (MRL 2024)</t>
-  </si>
-  <si>
-    <t>ruT5 / ruBERT (Zmitrovich и др.)</t>
-  </si>
-  <si>
-    <t>PAE</t>
-  </si>
-  <si>
-    <t>Habr, ecom.tech</t>
-  </si>
-  <si>
-    <t>UIE (ACL 2022)</t>
-  </si>
-  <si>
-    <t>OA-Mine (WWW 2022)</t>
-  </si>
-  <si>
-    <t>GPT-3 (NeurIPS 2020)</t>
-  </si>
-  <si>
-    <t>Parallel Decoding (Amazon)</t>
-  </si>
-  <si>
-    <t>статью отозвали, в таблице 6 ошибка</t>
-  </si>
-  <si>
-    <t>модели общего назначения, про атрибуты ничего</t>
-  </si>
-  <si>
-    <t>извлекает из PDF с трендами моды, а не из описаний</t>
-  </si>
-  <si>
-    <t>про сопоставление товаров, не про извлечение</t>
-  </si>
-  <si>
-    <t>общее извлечение, не про товары</t>
-  </si>
-  <si>
-    <t>атрибуты заранее не заданы, а у нас заданы</t>
-  </si>
-  <si>
-    <t>общий фон, few-shot смотрим в ExtractGPT</t>
-  </si>
-  <si>
-    <t>нет даты и площадки, данные закрыты</t>
+    <t>почему</t>
   </si>
   <si>
     <t>Qwen2.5-1M</t>
@@ -493,6 +514,132 @@
   </si>
   <si>
     <t>статья STIL</t>
+  </si>
+  <si>
+    <t>Attribute Extraction for E-Commerce Fashion Data (глава Springer)</t>
+  </si>
+  <si>
+    <t>Visual Zero-Shot E-Commerce Product Attribute Value Extraction (arXiv)</t>
+  </si>
+  <si>
+    <t>Product Attribute Extraction and Product Listing Analysis from E-commerce Websites (ResearchGate)</t>
+  </si>
+  <si>
+    <t>Aspect Extraction from E-Commerce Product and Service Reviews (arXiv)</t>
+  </si>
+  <si>
+    <t>Extract-0 (arXiv)</t>
+  </si>
+  <si>
+    <t>Structured Knowledge Extraction from Text using LLMs (магистерская работа, Росток)</t>
+  </si>
+  <si>
+    <t>A Robust Framework For Data Extraction From Unstructured Sources Using LLMs (doria.fi)</t>
+  </si>
+  <si>
+    <t>Attribute Value Extraction Based on Rule Matching (глава Springer)</t>
+  </si>
+  <si>
+    <t>Annotating aspects in text and image (JASIST)</t>
+  </si>
+  <si>
+    <t>Fusing Attribute Type Features for AVE via Question Answering (ACM)</t>
+  </si>
+  <si>
+    <t>LLM-Ensemble (SIGIR 2024)</t>
+  </si>
+  <si>
+    <t>Product Information Extraction using ChatGPT (arXiv 2023)</t>
+  </si>
+  <si>
+    <t>Self-Refinement Strategies for LLM-based PAVE (arXiv 2025)</t>
+  </si>
+  <si>
+    <t>AI-PAVE-Br (arXiv 2026)</t>
+  </si>
+  <si>
+    <t>вторичное по теме</t>
+  </si>
+  <si>
+    <t>по названию: не журнал, домен мода</t>
+  </si>
+  <si>
+    <t>по названию: мультимодальное, у нас только текст</t>
+  </si>
+  <si>
+    <t>по названию: не рецензируемая площадка, тема не про LLM</t>
+  </si>
+  <si>
+    <t>по названию: отзывы, другая задача</t>
+  </si>
+  <si>
+    <t>по названию: извлечение из документов, не из товаров</t>
+  </si>
+  <si>
+    <t>по названию: студенческая работа, не рецензируется</t>
+  </si>
+  <si>
+    <t>по названию: правила, старый подход, не журнал</t>
+  </si>
+  <si>
+    <t>по названию: аспекты, текст и изображения, другая задача</t>
+  </si>
+  <si>
+    <t>по названию: QA-подход, как AVEQA/MAVE; в запас</t>
+  </si>
+  <si>
+    <t>по названию: ансамбль LLM для извлечения, в запас, близко к ExtractGPT; можно открыть</t>
+  </si>
+  <si>
+    <t>по названию: ранняя версия линии ExtractGPT, в запас</t>
+  </si>
+  <si>
+    <t>по названию: исправление ошибок LLM после извлечения, в запас; можно открыть</t>
+  </si>
+  <si>
+    <t>не открыл: сервер вернул 429; в названии 'Leveraging LLMs for ...', возможно не английский язык, ОТКРЫТЬ вручную</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/chapter/10.1007/978-3-032-15996-0_11</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2502.15979</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/371348902_Product_Attribute_Extraction_and_Product_Listing_Analysis_from_E-commerce_Websites</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2601.01827v1</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2509.22906v1</t>
+  </si>
+  <si>
+    <t>https://eprints.dbis.informatik.uni-rostock.de/1121/</t>
+  </si>
+  <si>
+    <t>https://doria.fi/handle/10024/192883</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/chapter/10.1007/978-981-15-8101-4_10</t>
+  </si>
+  <si>
+    <t>https://asistdl.onlinelibrary.wiley.com/doi/pdfdirect/10.1002/asi.70026</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3578741.3578778</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3626772.3661357</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2306.14921</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2501.01237</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2606.24655</t>
   </si>
 </sst>
 </file>
@@ -837,39 +984,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -880,28 +1027,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -912,28 +1059,28 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -944,28 +1091,28 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -976,28 +1123,28 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1008,28 +1155,28 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1040,28 +1187,28 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1072,28 +1219,28 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1104,28 +1251,28 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1136,28 +1283,28 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1168,28 +1315,28 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1200,28 +1347,28 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I12" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1232,28 +1379,28 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1264,28 +1411,28 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1296,60 +1443,28 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" t="s">
-        <v>122</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1368,7 +1483,6 @@
     <hyperlink ref="J13" r:id="rId12"/>
     <hyperlink ref="J14" r:id="rId13"/>
     <hyperlink ref="J15" r:id="rId14"/>
-    <hyperlink ref="J16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1376,112 +1490,362 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>139</v>
       </c>
-      <c r="B1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>140</v>
       </c>
-      <c r="B2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>141</v>
       </c>
-      <c r="B3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>142</v>
       </c>
-      <c r="B4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="B13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>143</v>
       </c>
-      <c r="B5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" t="s">
-        <v>155</v>
+      <c r="B14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C10" r:id="rId1"/>
+    <hyperlink ref="C11" r:id="rId2"/>
+    <hyperlink ref="C12" r:id="rId3"/>
+    <hyperlink ref="C13" r:id="rId4"/>
+    <hyperlink ref="C14" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A5"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>163</v>
+      </c>
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>165</v>
+      </c>
+      <c r="B4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="C6" r:id="rId2"/>
+    <hyperlink ref="C7" r:id="rId3"/>
+    <hyperlink ref="C8" r:id="rId4"/>
+    <hyperlink ref="C9" r:id="rId5"/>
+    <hyperlink ref="C10" r:id="rId6"/>
+    <hyperlink ref="C11" r:id="rId7"/>
+    <hyperlink ref="C12" r:id="rId8"/>
+    <hyperlink ref="C13" r:id="rId9"/>
+    <hyperlink ref="C14" r:id="rId10"/>
+    <hyperlink ref="C15" r:id="rId11"/>
+    <hyperlink ref="C16" r:id="rId12"/>
+    <hyperlink ref="C17" r:id="rId13"/>
+    <hyperlink ref="C18" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>